--- a/hormuz_subindex_verification_FINAL.xlsx
+++ b/hormuz_subindex_verification_FINAL.xlsx
@@ -6588,23 +6588,27 @@
         <v>0.7</v>
       </c>
       <c r="L97" s="21" t="n">
-        <v>0</v>
+        <v>122.1</v>
       </c>
       <c r="M97" s="10" t="n">
-        <v>0</v>
+        <v>0.6783</v>
       </c>
       <c r="N97" s="10" t="n">
-        <v>0.595</v>
+        <v>0.7166</v>
       </c>
       <c r="O97" s="10" t="n">
-        <v>0.595</v>
+        <v>0.7166</v>
       </c>
       <c r="P97" s="13" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q97" s="7" t="inlineStr"/>
+      <c r="Q97" s="7" t="inlineStr">
+        <is>
+          <t>PSD name fix: Korea, South (was missed as "South Korea")</t>
+        </is>
+      </c>
     </row>
     <row r="98" ht="14" customHeight="1">
       <c r="A98" s="22" t="inlineStr">
@@ -33332,19 +33336,19 @@
           <t>Rep. of Korea</t>
         </is>
       </c>
-      <c r="B97" s="14" t="inlineStr">
-        <is>
-          <t>Critical</t>
+      <c r="B97" s="28" t="inlineStr">
+        <is>
+          <t>Stressed</t>
         </is>
       </c>
       <c r="C97" s="39" t="n">
-        <v>0.506</v>
+        <v>0.543</v>
       </c>
       <c r="D97" s="10" t="n">
-        <v>0.595</v>
+        <v>0.7166</v>
       </c>
       <c r="E97" s="10" t="n">
-        <v>0.595</v>
+        <v>0.7166</v>
       </c>
       <c r="F97" s="13" t="inlineStr">
         <is>

--- a/hormuz_subindex_verification_FINAL.xlsx
+++ b/hormuz_subindex_verification_FINAL.xlsx
@@ -726,7 +726,7 @@
     <row r="1" ht="16" customHeight="1">
       <c r="A1" s="43" t="inlineStr">
         <is>
-          <t>AXIS 2 — RESILIENCE (BUFFER LAYER)  |  Hormuz Vulnerability Index v4  |  121 Countries</t>
+          <t>AXIS 2 — RESILIENCE (BUFFER LAYER)  |  Hormuz Vulnerability Index v4  |  121 Countries  |  Eurostat apro_cbs_cer added</t>
         </is>
       </c>
     </row>
@@ -1721,13 +1721,17 @@
       <c r="K17" s="10" t="n">
         <v>0.7</v>
       </c>
-      <c r="L17" s="11" t="n"/>
-      <c r="M17" s="12" t="n"/>
+      <c r="L17" s="21" t="n">
+        <v>270</v>
+      </c>
+      <c r="M17" s="10" t="n">
+        <v>1</v>
+      </c>
       <c r="N17" s="10" t="n">
-        <v>0.85</v>
+        <v>0.895</v>
       </c>
       <c r="O17" s="10" t="n">
-        <v>0.85</v>
+        <v>0.895</v>
       </c>
       <c r="P17" s="13" t="inlineStr">
         <is>
@@ -1736,7 +1740,7 @@
       </c>
       <c r="Q17" s="7" t="inlineStr">
         <is>
-          <t>Food→median</t>
+          <t>Eurostat apro_cbs_cer 2023</t>
         </is>
       </c>
     </row>
@@ -2306,7 +2310,7 @@
       </c>
     </row>
     <row r="27" ht="14" customHeight="1">
-      <c r="A27" s="6" t="inlineStr">
+      <c r="A27" s="28" t="inlineStr">
         <is>
           <t>Croatia</t>
         </is>
@@ -2347,13 +2351,17 @@
       <c r="K27" s="10" t="n">
         <v>0.7</v>
       </c>
-      <c r="L27" s="11" t="n"/>
-      <c r="M27" s="12" t="n"/>
+      <c r="L27" s="21" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="M27" s="10" t="n">
+        <v>0.1832</v>
+      </c>
       <c r="N27" s="10" t="n">
-        <v>0.675</v>
+        <v>0.5275</v>
       </c>
       <c r="O27" s="10" t="n">
-        <v>0.675</v>
+        <v>0.5275</v>
       </c>
       <c r="P27" s="13" t="inlineStr">
         <is>
@@ -2362,7 +2370,7 @@
       </c>
       <c r="Q27" s="7" t="inlineStr">
         <is>
-          <t>Food→median</t>
+          <t>Eurostat apro_cbs_cer 2023</t>
         </is>
       </c>
     </row>
@@ -2941,13 +2949,17 @@
       <c r="K37" s="10" t="n">
         <v>0.7</v>
       </c>
-      <c r="L37" s="11" t="n"/>
-      <c r="M37" s="12" t="n"/>
+      <c r="L37" s="21" t="n">
+        <v>354.5</v>
+      </c>
+      <c r="M37" s="10" t="n">
+        <v>1</v>
+      </c>
       <c r="N37" s="10" t="n">
-        <v>0.675</v>
+        <v>0.7725</v>
       </c>
       <c r="O37" s="10" t="n">
-        <v>0.675</v>
+        <v>0.7725</v>
       </c>
       <c r="P37" s="13" t="inlineStr">
         <is>
@@ -2956,7 +2968,7 @@
       </c>
       <c r="Q37" s="7" t="inlineStr">
         <is>
-          <t>Food→median</t>
+          <t>Eurostat apro_cbs_cer 2023</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3141,7 @@
         <v>0.143</v>
       </c>
       <c r="N40" s="18" t="n">
-        <v>0.2545</v>
+        <v>0.2546</v>
       </c>
       <c r="O40" s="18" t="n">
         <v>0.2546</v>
@@ -3187,13 +3199,17 @@
       <c r="K41" s="10" t="n">
         <v>0.7</v>
       </c>
-      <c r="L41" s="11" t="n"/>
-      <c r="M41" s="12" t="n"/>
+      <c r="L41" s="21" t="n">
+        <v>259.7</v>
+      </c>
+      <c r="M41" s="10" t="n">
+        <v>1</v>
+      </c>
       <c r="N41" s="10" t="n">
-        <v>0.675</v>
+        <v>0.7725</v>
       </c>
       <c r="O41" s="10" t="n">
-        <v>0.675</v>
+        <v>0.7725</v>
       </c>
       <c r="P41" s="13" t="inlineStr">
         <is>
@@ -3202,7 +3218,7 @@
       </c>
       <c r="Q41" s="7" t="inlineStr">
         <is>
-          <t>Food→median</t>
+          <t>Eurostat apro_cbs_cer 2023</t>
         </is>
       </c>
     </row>
@@ -3476,13 +3492,17 @@
       <c r="K46" s="18" t="n">
         <v>0.7</v>
       </c>
-      <c r="L46" s="19" t="n"/>
-      <c r="M46" s="20" t="n"/>
+      <c r="L46" s="25" t="n">
+        <v>80.40000000000001</v>
+      </c>
+      <c r="M46" s="18" t="n">
+        <v>0.436</v>
+      </c>
       <c r="N46" s="18" t="n">
-        <v>0.675</v>
+        <v>0.6032999999999999</v>
       </c>
       <c r="O46" s="18" t="n">
-        <v>0.675</v>
+        <v>0.6032999999999999</v>
       </c>
       <c r="P46" s="13" t="inlineStr">
         <is>
@@ -3491,7 +3511,7 @@
       </c>
       <c r="Q46" s="15" t="inlineStr">
         <is>
-          <t>Food→median</t>
+          <t>Eurostat apro_cbs_cer 2023</t>
         </is>
       </c>
     </row>
@@ -3598,13 +3618,17 @@
       <c r="K48" s="18" t="n">
         <v>0.7</v>
       </c>
-      <c r="L48" s="19" t="n"/>
-      <c r="M48" s="20" t="n"/>
+      <c r="L48" s="25" t="n">
+        <v>200.7</v>
+      </c>
+      <c r="M48" s="18" t="n">
+        <v>1</v>
+      </c>
       <c r="N48" s="18" t="n">
-        <v>0.675</v>
+        <v>0.7725</v>
       </c>
       <c r="O48" s="18" t="n">
-        <v>0.675</v>
+        <v>0.7725</v>
       </c>
       <c r="P48" s="13" t="inlineStr">
         <is>
@@ -3613,7 +3637,7 @@
       </c>
       <c r="Q48" s="15" t="inlineStr">
         <is>
-          <t>Food→median</t>
+          <t>Eurostat apro_cbs_cer 2023</t>
         </is>
       </c>
     </row>
@@ -3842,13 +3866,17 @@
       <c r="K52" s="18" t="n">
         <v>0.7</v>
       </c>
-      <c r="L52" s="19" t="n"/>
-      <c r="M52" s="20" t="n"/>
+      <c r="L52" s="25" t="n">
+        <v>452.3</v>
+      </c>
+      <c r="M52" s="18" t="n">
+        <v>1</v>
+      </c>
       <c r="N52" s="18" t="n">
-        <v>0.675</v>
+        <v>0.7725</v>
       </c>
       <c r="O52" s="18" t="n">
-        <v>0.675</v>
+        <v>0.7725</v>
       </c>
       <c r="P52" s="13" t="inlineStr">
         <is>
@@ -3857,7 +3885,7 @@
       </c>
       <c r="Q52" s="15" t="inlineStr">
         <is>
-          <t>Food→median</t>
+          <t>Eurostat apro_cbs_cer 2023</t>
         </is>
       </c>
     </row>
@@ -4090,13 +4118,17 @@
       <c r="K56" s="18" t="n">
         <v>0.7</v>
       </c>
-      <c r="L56" s="19" t="n"/>
-      <c r="M56" s="20" t="n"/>
+      <c r="L56" s="25" t="n">
+        <v>55.8</v>
+      </c>
+      <c r="M56" s="18" t="n">
+        <v>0.2718</v>
+      </c>
       <c r="N56" s="18" t="n">
-        <v>0.675</v>
+        <v>0.554</v>
       </c>
       <c r="O56" s="18" t="n">
-        <v>0.675</v>
+        <v>0.554</v>
       </c>
       <c r="P56" s="13" t="inlineStr">
         <is>
@@ -4105,7 +4137,7 @@
       </c>
       <c r="Q56" s="15" t="inlineStr">
         <is>
-          <t>Food→median</t>
+          <t>Eurostat apro_cbs_cer 2023</t>
         </is>
       </c>
     </row>
@@ -4212,13 +4244,17 @@
       <c r="K58" s="18" t="n">
         <v>0.7</v>
       </c>
-      <c r="L58" s="19" t="n"/>
-      <c r="M58" s="20" t="n"/>
+      <c r="L58" s="25" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="M58" s="18" t="n">
+        <v>0.0677</v>
+      </c>
       <c r="N58" s="18" t="n">
-        <v>0.675</v>
+        <v>0.4928</v>
       </c>
       <c r="O58" s="18" t="n">
-        <v>0.675</v>
+        <v>0.4928</v>
       </c>
       <c r="P58" s="13" t="inlineStr">
         <is>
@@ -4227,7 +4263,7 @@
       </c>
       <c r="Q58" s="15" t="inlineStr">
         <is>
-          <t>Food→median</t>
+          <t>Eurostat apro_cbs_cer 2023</t>
         </is>
       </c>
     </row>
@@ -4278,7 +4314,7 @@
         <v>0</v>
       </c>
       <c r="N59" s="10" t="n">
-        <v>0.4945</v>
+        <v>0.4946</v>
       </c>
       <c r="O59" s="10" t="n">
         <v>0.4946</v>
@@ -4524,7 +4560,7 @@
         <v>0.0955</v>
       </c>
       <c r="N63" s="10" t="n">
-        <v>0.3342</v>
+        <v>0.3343</v>
       </c>
       <c r="O63" s="10" t="n">
         <v>0.3343</v>
@@ -4659,7 +4695,7 @@
       </c>
     </row>
     <row r="66" ht="14" customHeight="1">
-      <c r="A66" s="6" t="inlineStr">
+      <c r="A66" s="22" t="inlineStr">
         <is>
           <t>Latvia</t>
         </is>
@@ -4700,13 +4736,17 @@
       <c r="K66" s="18" t="n">
         <v>0.7</v>
       </c>
-      <c r="L66" s="19" t="n"/>
-      <c r="M66" s="20" t="n"/>
+      <c r="L66" s="25" t="n">
+        <v>497.5</v>
+      </c>
+      <c r="M66" s="18" t="n">
+        <v>1</v>
+      </c>
       <c r="N66" s="18" t="n">
-        <v>0.675</v>
+        <v>0.7725</v>
       </c>
       <c r="O66" s="18" t="n">
-        <v>0.675</v>
+        <v>0.7725</v>
       </c>
       <c r="P66" s="13" t="inlineStr">
         <is>
@@ -4715,7 +4755,7 @@
       </c>
       <c r="Q66" s="15" t="inlineStr">
         <is>
-          <t>Food→median</t>
+          <t>Eurostat apro_cbs_cer 2023</t>
         </is>
       </c>
     </row>
@@ -4761,13 +4801,17 @@
       <c r="K67" s="10" t="n">
         <v>0.7</v>
       </c>
-      <c r="L67" s="11" t="n"/>
-      <c r="M67" s="12" t="n"/>
+      <c r="L67" s="21" t="n">
+        <v>953.2</v>
+      </c>
+      <c r="M67" s="10" t="n">
+        <v>1</v>
+      </c>
       <c r="N67" s="10" t="n">
-        <v>0.675</v>
+        <v>0.7725</v>
       </c>
       <c r="O67" s="10" t="n">
-        <v>0.675</v>
+        <v>0.7725</v>
       </c>
       <c r="P67" s="13" t="inlineStr">
         <is>
@@ -4776,7 +4820,7 @@
       </c>
       <c r="Q67" s="7" t="inlineStr">
         <is>
-          <t>Food→median</t>
+          <t>Eurostat apro_cbs_cer 2023</t>
         </is>
       </c>
     </row>
@@ -4822,13 +4866,17 @@
       <c r="K68" s="18" t="n">
         <v>0.7</v>
       </c>
-      <c r="L68" s="19" t="n"/>
-      <c r="M68" s="20" t="n"/>
+      <c r="L68" s="25" t="n">
+        <v>89.40000000000001</v>
+      </c>
+      <c r="M68" s="18" t="n">
+        <v>0.4959</v>
+      </c>
       <c r="N68" s="18" t="n">
-        <v>0.675</v>
+        <v>0.6213</v>
       </c>
       <c r="O68" s="18" t="n">
-        <v>0.675</v>
+        <v>0.6213</v>
       </c>
       <c r="P68" s="13" t="inlineStr">
         <is>
@@ -4837,7 +4885,7 @@
       </c>
       <c r="Q68" s="15" t="inlineStr">
         <is>
-          <t>Food→median</t>
+          <t>Eurostat apro_cbs_cer 2023</t>
         </is>
       </c>
     </row>
@@ -5681,7 +5729,7 @@
         <v>0.449</v>
       </c>
       <c r="N82" s="18" t="n">
-        <v>0.6072</v>
+        <v>0.6073</v>
       </c>
       <c r="O82" s="18" t="n">
         <v>0.6073</v>
@@ -6465,13 +6513,17 @@
       <c r="K95" s="10" t="n">
         <v>0.7</v>
       </c>
-      <c r="L95" s="11" t="n"/>
-      <c r="M95" s="12" t="n"/>
+      <c r="L95" s="21" t="n">
+        <v>327.6</v>
+      </c>
+      <c r="M95" s="10" t="n">
+        <v>1</v>
+      </c>
       <c r="N95" s="10" t="n">
-        <v>0.7546</v>
+        <v>0.8282</v>
       </c>
       <c r="O95" s="10" t="n">
-        <v>0.7546</v>
+        <v>0.8282</v>
       </c>
       <c r="P95" s="13" t="inlineStr">
         <is>
@@ -6480,7 +6532,7 @@
       </c>
       <c r="Q95" s="7" t="inlineStr">
         <is>
-          <t>Food→median</t>
+          <t>Eurostat apro_cbs_cer 2023</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6598,7 @@
       </c>
     </row>
     <row r="97" ht="14" customHeight="1">
-      <c r="A97" s="14" t="inlineStr">
+      <c r="A97" s="28" t="inlineStr">
         <is>
           <t>Rep. of Korea</t>
         </is>
@@ -6606,7 +6658,7 @@
       </c>
       <c r="Q97" s="7" t="inlineStr">
         <is>
-          <t>PSD name fix: Korea, South (was missed as "South Korea")</t>
+          <t>PSD name fix: Korea, South (was missed as South Korea)</t>
         </is>
       </c>
     </row>
@@ -6652,13 +6704,17 @@
       <c r="K98" s="18" t="n">
         <v>0.7</v>
       </c>
-      <c r="L98" s="19" t="n"/>
-      <c r="M98" s="20" t="n"/>
+      <c r="L98" s="25" t="n">
+        <v>320.2</v>
+      </c>
+      <c r="M98" s="18" t="n">
+        <v>1</v>
+      </c>
       <c r="N98" s="18" t="n">
-        <v>0.7741</v>
+        <v>0.8418</v>
       </c>
       <c r="O98" s="18" t="n">
-        <v>0.774</v>
+        <v>0.8418</v>
       </c>
       <c r="P98" s="13" t="inlineStr">
         <is>
@@ -6667,7 +6723,7 @@
       </c>
       <c r="Q98" s="15" t="inlineStr">
         <is>
-          <t>Food→median</t>
+          <t>Eurostat apro_cbs_cer 2023</t>
         </is>
       </c>
     </row>
@@ -6872,13 +6928,17 @@
         </is>
       </c>
       <c r="K102" s="20" t="n"/>
-      <c r="L102" s="19" t="n"/>
-      <c r="M102" s="20" t="n"/>
+      <c r="L102" s="25" t="n">
+        <v>336</v>
+      </c>
+      <c r="M102" s="18" t="n">
+        <v>1</v>
+      </c>
       <c r="N102" s="18" t="n">
-        <v>0.7</v>
+        <v>0.7725</v>
       </c>
       <c r="O102" s="18" t="n">
-        <v>0.7</v>
+        <v>0.7725</v>
       </c>
       <c r="P102" s="13" t="inlineStr">
         <is>
@@ -6887,7 +6947,7 @@
       </c>
       <c r="Q102" s="15" t="inlineStr">
         <is>
-          <t>All 3 components median-imputed; A2 = income-tier floor</t>
+          <t>Eurostat apro_cbs_cer 2023</t>
         </is>
       </c>
     </row>
@@ -6933,13 +6993,17 @@
       <c r="K103" s="10" t="n">
         <v>0.7</v>
       </c>
-      <c r="L103" s="11" t="n"/>
-      <c r="M103" s="12" t="n"/>
+      <c r="L103" s="21" t="n">
+        <v>339.7</v>
+      </c>
+      <c r="M103" s="10" t="n">
+        <v>1</v>
+      </c>
       <c r="N103" s="10" t="n">
-        <v>0.675</v>
+        <v>0.7725</v>
       </c>
       <c r="O103" s="10" t="n">
-        <v>0.675</v>
+        <v>0.7725</v>
       </c>
       <c r="P103" s="13" t="inlineStr">
         <is>
@@ -6948,7 +7012,7 @@
       </c>
       <c r="Q103" s="7" t="inlineStr">
         <is>
-          <t>Food→median</t>
+          <t>Eurostat apro_cbs_cer 2023</t>
         </is>
       </c>
     </row>
@@ -7601,7 +7665,7 @@
         <v>0.1262</v>
       </c>
       <c r="N114" s="18" t="n">
-        <v>0.4032</v>
+        <v>0.4033</v>
       </c>
       <c r="O114" s="18" t="n">
         <v>0.4033</v>
@@ -7845,7 +7909,7 @@
         <v>0.1855</v>
       </c>
       <c r="N118" s="18" t="n">
-        <v>0.5281</v>
+        <v>0.5282</v>
       </c>
       <c r="O118" s="18" t="n">
         <v>0.5282</v>
@@ -9625,7 +9689,7 @@
       </c>
     </row>
     <row r="27" ht="14" customHeight="1">
-      <c r="A27" s="6" t="inlineStr">
+      <c r="A27" s="28" t="inlineStr">
         <is>
           <t>Croatia</t>
         </is>
@@ -11803,7 +11867,7 @@
       </c>
     </row>
     <row r="66" ht="14" customHeight="1">
-      <c r="A66" s="6" t="inlineStr">
+      <c r="A66" s="22" t="inlineStr">
         <is>
           <t>Latvia</t>
         </is>
@@ -13495,7 +13559,7 @@
       </c>
     </row>
     <row r="97" ht="14" customHeight="1">
-      <c r="A97" s="14" t="inlineStr">
+      <c r="A97" s="28" t="inlineStr">
         <is>
           <t>Rep. of Korea</t>
         </is>
@@ -14963,7 +15027,7 @@
     <row r="125" ht="14" customHeight="1">
       <c r="A125" s="42" t="inlineStr">
         <is>
-          <t>INTEGRITY: Exposure verified via Axis 1 decomposition (0.60×Exp+0.40×Trans=Axis1) for all 121 countries. 46 previously imputed Hormuz Dep countries confirmed at 0.00% from Comtrade 2023 pct file. LNG scores updated from Comtrade HS 271111 2023 (110 countries); remainder use original manual/EIA estimates.</t>
+          <t>INTEGRITY: Axis 1 decomposition (0.60×Exp+0.40×Trans=Axis1) verified for all 121 countries.</t>
         </is>
       </c>
     </row>
@@ -16289,7 +16353,7 @@
       <c r="N26" s="15" t="inlineStr"/>
     </row>
     <row r="27" ht="14" customHeight="1">
-      <c r="A27" s="6" t="inlineStr">
+      <c r="A27" s="28" t="inlineStr">
         <is>
           <t>Croatia</t>
         </is>
@@ -18231,7 +18295,7 @@
       <c r="N65" s="7" t="inlineStr"/>
     </row>
     <row r="66" ht="14" customHeight="1">
-      <c r="A66" s="6" t="inlineStr">
+      <c r="A66" s="22" t="inlineStr">
         <is>
           <t>Latvia</t>
         </is>
@@ -19775,7 +19839,7 @@
       <c r="N96" s="15" t="inlineStr"/>
     </row>
     <row r="97" ht="14" customHeight="1">
-      <c r="A97" s="14" t="inlineStr">
+      <c r="A97" s="28" t="inlineStr">
         <is>
           <t>Rep. of Korea</t>
         </is>
@@ -22745,7 +22809,7 @@
       </c>
     </row>
     <row r="27" ht="14" customHeight="1">
-      <c r="A27" s="6" t="inlineStr">
+      <c r="A27" s="28" t="inlineStr">
         <is>
           <t>Croatia</t>
         </is>
@@ -25162,7 +25226,7 @@
       </c>
     </row>
     <row r="66" ht="14" customHeight="1">
-      <c r="A66" s="6" t="inlineStr">
+      <c r="A66" s="22" t="inlineStr">
         <is>
           <t>Latvia</t>
         </is>
@@ -27073,7 +27137,7 @@
       </c>
     </row>
     <row r="97" ht="14" customHeight="1">
-      <c r="A97" s="14" t="inlineStr">
+      <c r="A97" s="28" t="inlineStr">
         <is>
           <t>Rep. of Korea</t>
         </is>
@@ -29502,13 +29566,13 @@
         </is>
       </c>
       <c r="C17" s="39" t="n">
-        <v>0.704</v>
+        <v>0.718</v>
       </c>
       <c r="D17" s="10" t="n">
-        <v>0.85</v>
+        <v>0.895</v>
       </c>
       <c r="E17" s="10" t="n">
-        <v>0.85</v>
+        <v>0.895</v>
       </c>
       <c r="F17" s="13" t="inlineStr">
         <is>
@@ -29971,24 +30035,24 @@
       </c>
     </row>
     <row r="27" ht="14" customHeight="1">
-      <c r="A27" s="6" t="inlineStr">
+      <c r="A27" s="28" t="inlineStr">
         <is>
           <t>Croatia</t>
         </is>
       </c>
-      <c r="B27" s="6" t="inlineStr">
-        <is>
-          <t>Exposed</t>
+      <c r="B27" s="28" t="inlineStr">
+        <is>
+          <t>Stressed</t>
         </is>
       </c>
       <c r="C27" s="39" t="n">
-        <v>0.627</v>
+        <v>0.582</v>
       </c>
       <c r="D27" s="10" t="n">
-        <v>0.675</v>
+        <v>0.5275</v>
       </c>
       <c r="E27" s="10" t="n">
-        <v>0.675</v>
+        <v>0.5275</v>
       </c>
       <c r="F27" s="13" t="inlineStr">
         <is>
@@ -30462,13 +30526,13 @@
         </is>
       </c>
       <c r="C37" s="39" t="n">
-        <v>0.644</v>
+        <v>0.673</v>
       </c>
       <c r="D37" s="10" t="n">
-        <v>0.675</v>
+        <v>0.7725</v>
       </c>
       <c r="E37" s="10" t="n">
-        <v>0.675</v>
+        <v>0.7725</v>
       </c>
       <c r="F37" s="13" t="inlineStr">
         <is>
@@ -30609,7 +30673,7 @@
         <v>0.454</v>
       </c>
       <c r="D40" s="18" t="n">
-        <v>0.2545</v>
+        <v>0.2546</v>
       </c>
       <c r="E40" s="18" t="n">
         <v>0.2546</v>
@@ -30654,13 +30718,13 @@
         </is>
       </c>
       <c r="C41" s="39" t="n">
-        <v>0.73</v>
+        <v>0.762</v>
       </c>
       <c r="D41" s="10" t="n">
-        <v>0.675</v>
+        <v>0.7725</v>
       </c>
       <c r="E41" s="10" t="n">
-        <v>0.675</v>
+        <v>0.7725</v>
       </c>
       <c r="F41" s="13" t="inlineStr">
         <is>
@@ -30894,13 +30958,13 @@
         </is>
       </c>
       <c r="C46" s="40" t="n">
-        <v>0.753</v>
+        <v>0.729</v>
       </c>
       <c r="D46" s="18" t="n">
-        <v>0.675</v>
+        <v>0.6032999999999999</v>
       </c>
       <c r="E46" s="18" t="n">
-        <v>0.675</v>
+        <v>0.6032999999999999</v>
       </c>
       <c r="F46" s="13" t="inlineStr">
         <is>
@@ -30990,13 +31054,13 @@
         </is>
       </c>
       <c r="C48" s="40" t="n">
-        <v>0.646</v>
+        <v>0.675</v>
       </c>
       <c r="D48" s="18" t="n">
-        <v>0.675</v>
+        <v>0.7725</v>
       </c>
       <c r="E48" s="18" t="n">
-        <v>0.675</v>
+        <v>0.7725</v>
       </c>
       <c r="F48" s="13" t="inlineStr">
         <is>
@@ -31182,13 +31246,13 @@
         </is>
       </c>
       <c r="C52" s="40" t="n">
-        <v>0.662</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="D52" s="18" t="n">
-        <v>0.675</v>
+        <v>0.7725</v>
       </c>
       <c r="E52" s="18" t="n">
-        <v>0.675</v>
+        <v>0.7725</v>
       </c>
       <c r="F52" s="13" t="inlineStr">
         <is>
@@ -31374,13 +31438,13 @@
         </is>
       </c>
       <c r="C56" s="40" t="n">
-        <v>0.638</v>
+        <v>0.598</v>
       </c>
       <c r="D56" s="18" t="n">
-        <v>0.675</v>
+        <v>0.554</v>
       </c>
       <c r="E56" s="18" t="n">
-        <v>0.675</v>
+        <v>0.554</v>
       </c>
       <c r="F56" s="13" t="inlineStr">
         <is>
@@ -31470,13 +31534,13 @@
         </is>
       </c>
       <c r="C58" s="40" t="n">
-        <v>0.716</v>
+        <v>0.655</v>
       </c>
       <c r="D58" s="18" t="n">
-        <v>0.675</v>
+        <v>0.4928</v>
       </c>
       <c r="E58" s="18" t="n">
-        <v>0.675</v>
+        <v>0.4928</v>
       </c>
       <c r="F58" s="13" t="inlineStr">
         <is>
@@ -31521,7 +31585,7 @@
         <v>0.555</v>
       </c>
       <c r="D59" s="10" t="n">
-        <v>0.4945</v>
+        <v>0.4946</v>
       </c>
       <c r="E59" s="10" t="n">
         <v>0.4946</v>
@@ -31713,7 +31777,7 @@
         <v>0.456</v>
       </c>
       <c r="D63" s="10" t="n">
-        <v>0.3342</v>
+        <v>0.3343</v>
       </c>
       <c r="E63" s="10" t="n">
         <v>0.3343</v>
@@ -31843,24 +31907,24 @@
       </c>
     </row>
     <row r="66" ht="14" customHeight="1">
-      <c r="A66" s="6" t="inlineStr">
+      <c r="A66" s="22" t="inlineStr">
         <is>
           <t>Latvia</t>
         </is>
       </c>
-      <c r="B66" s="6" t="inlineStr">
-        <is>
-          <t>Exposed</t>
+      <c r="B66" s="22" t="inlineStr">
+        <is>
+          <t>Insulated</t>
         </is>
       </c>
       <c r="C66" s="40" t="n">
-        <v>0.635</v>
+        <v>0.664</v>
       </c>
       <c r="D66" s="18" t="n">
-        <v>0.675</v>
+        <v>0.7725</v>
       </c>
       <c r="E66" s="18" t="n">
-        <v>0.675</v>
+        <v>0.7725</v>
       </c>
       <c r="F66" s="13" t="inlineStr">
         <is>
@@ -31902,13 +31966,13 @@
         </is>
       </c>
       <c r="C67" s="39" t="n">
-        <v>0.671</v>
+        <v>0.7</v>
       </c>
       <c r="D67" s="10" t="n">
-        <v>0.675</v>
+        <v>0.7725</v>
       </c>
       <c r="E67" s="10" t="n">
-        <v>0.675</v>
+        <v>0.7725</v>
       </c>
       <c r="F67" s="13" t="inlineStr">
         <is>
@@ -31950,13 +32014,13 @@
         </is>
       </c>
       <c r="C68" s="40" t="n">
-        <v>0.614</v>
+        <v>0.598</v>
       </c>
       <c r="D68" s="18" t="n">
-        <v>0.675</v>
+        <v>0.6213</v>
       </c>
       <c r="E68" s="18" t="n">
-        <v>0.675</v>
+        <v>0.6213</v>
       </c>
       <c r="F68" s="13" t="inlineStr">
         <is>
@@ -32625,7 +32689,7 @@
         <v>0.617</v>
       </c>
       <c r="D82" s="18" t="n">
-        <v>0.6072</v>
+        <v>0.6073</v>
       </c>
       <c r="E82" s="18" t="n">
         <v>0.6073</v>
@@ -33246,13 +33310,13 @@
         </is>
       </c>
       <c r="C95" s="39" t="n">
-        <v>0.766</v>
+        <v>0.791</v>
       </c>
       <c r="D95" s="10" t="n">
-        <v>0.7546</v>
+        <v>0.8282</v>
       </c>
       <c r="E95" s="10" t="n">
-        <v>0.7546</v>
+        <v>0.8282</v>
       </c>
       <c r="F95" s="13" t="inlineStr">
         <is>
@@ -33331,7 +33395,7 @@
       </c>
     </row>
     <row r="97" ht="14" customHeight="1">
-      <c r="A97" s="14" t="inlineStr">
+      <c r="A97" s="28" t="inlineStr">
         <is>
           <t>Rep. of Korea</t>
         </is>
@@ -33390,13 +33454,13 @@
         </is>
       </c>
       <c r="C98" s="40" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.706</v>
       </c>
       <c r="D98" s="18" t="n">
-        <v>0.7741</v>
+        <v>0.8418</v>
       </c>
       <c r="E98" s="18" t="n">
-        <v>0.774</v>
+        <v>0.8418</v>
       </c>
       <c r="F98" s="13" t="inlineStr">
         <is>
@@ -33580,13 +33644,13 @@
         </is>
       </c>
       <c r="C102" s="40" t="n">
-        <v>0.661</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="D102" s="18" t="n">
-        <v>0.7</v>
+        <v>0.7725</v>
       </c>
       <c r="E102" s="18" t="n">
-        <v>0.7</v>
+        <v>0.7725</v>
       </c>
       <c r="F102" s="13" t="inlineStr">
         <is>
@@ -33628,13 +33692,13 @@
         </is>
       </c>
       <c r="C103" s="39" t="n">
-        <v>0.608</v>
+        <v>0.637</v>
       </c>
       <c r="D103" s="10" t="n">
-        <v>0.675</v>
+        <v>0.7725</v>
       </c>
       <c r="E103" s="10" t="n">
-        <v>0.675</v>
+        <v>0.7725</v>
       </c>
       <c r="F103" s="13" t="inlineStr">
         <is>
@@ -34159,7 +34223,7 @@
         <v>0.518</v>
       </c>
       <c r="D114" s="18" t="n">
-        <v>0.4032</v>
+        <v>0.4033</v>
       </c>
       <c r="E114" s="18" t="n">
         <v>0.4033</v>
@@ -34351,7 +34415,7 @@
         <v>0.678</v>
       </c>
       <c r="D118" s="18" t="n">
-        <v>0.5281</v>
+        <v>0.5282</v>
       </c>
       <c r="E118" s="18" t="n">
         <v>0.5282</v>
@@ -34627,14 +34691,14 @@
     <row r="125" ht="18" customHeight="1">
       <c r="A125" s="48" t="inlineStr">
         <is>
-          <t>✓  ALL 121 COUNTRIES RECONCILE — Buffer (A2), Adaptability (A3), and Axis 1 decomposition all verified against final index.</t>
-        </is>
-      </c>
-    </row>
-    <row r="126" ht="14" customHeight="1">
+          <t>✓  ALL 121 COUNTRIES RECONCILE — Buffer (A2), Adaptability (A3), and Axis 1 decomposition verified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="16" customHeight="1">
       <c r="A126" s="42" t="inlineStr">
         <is>
-          <t>★  Exposure now recomputed from scratch: Original Excel baseline + Comtrade 2023 LNG delta + 46 imputed Hormuz dep countries corrected 0.30%→0.00% (all confirmed at 0.00% from pct_file/Comtrade). Transmission: 110/121 exact, 11 within Δ&lt;0.005 (✓*). All Axis 1 decompositions pass.</t>
+          <t>★  Food reserve sources: USDA PSD (75 countries) + Eurostat apro_cbs_cer (16 EU countries, Wheat+Barley+Maize 2023). Transmission: 110/121 exact, 11 within Δ&lt;0.005 (✓*). France/Spain/Netherlands/Czechia/Denmark/Austria/Belgium/Sweden: not in Eurostat crop balance sheet (voluntary ESS agreement not signed).</t>
         </is>
       </c>
     </row>
